--- a/data/trans_dic/IP09B02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>81,26; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,59; 88,15</t>
+          <t>51,88; 87,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,32; 93,3</t>
+          <t>46,95; 93,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,49; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,49; 100,0</t>
+          <t>68,51; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,27; 85,58</t>
+          <t>46,1; 86,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,05; 91,05</t>
+          <t>34,74; 88,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>67,84; 100,0</t>
+          <t>74,34; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79,02; 100,0</t>
+          <t>79,47; 100,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55,12; 81,91</t>
+          <t>55,99; 82,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49,29; 86,81</t>
+          <t>48,38; 86,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,41; 100,0</t>
+          <t>85,13; 100,0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,12; 70,77</t>
+          <t>20,21; 70,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,12; 77,6</t>
+          <t>31,27; 77,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,61</t>
+          <t>0,0; 71,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,95; 95,04</t>
+          <t>41,31; 95,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,89; 100,0</t>
+          <t>64,76; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,6; 94,12</t>
+          <t>44,11; 94,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,24; 100,0</t>
+          <t>21,52; 100,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,99; 74,7</t>
+          <t>16,22; 75,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,28; 81,92</t>
+          <t>48,34; 81,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46,68; 79,76</t>
+          <t>46,35; 79,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,43; 75,52</t>
+          <t>18,97; 75,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,54; 77,87</t>
+          <t>35,83; 78,18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55,93; 100,0</t>
+          <t>62,07; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,76</t>
+          <t>0,0; 80,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63,9; 100,0</t>
+          <t>63,64; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,16; 77,88</t>
+          <t>11,31; 77,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,56</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,65; 92,21</t>
+          <t>43,14; 92,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,25; 86,51</t>
+          <t>46,54; 86,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,2; 65,59</t>
+          <t>8,85; 65,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>62,64; 95,53</t>
+          <t>59,49; 95,1</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,13; 100,0</t>
+          <t>43,05; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,41; 86,69</t>
+          <t>29,4; 84,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,56; 91,16</t>
+          <t>32,55; 90,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,01; 100,0</t>
+          <t>53,82; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,97; 81,07</t>
+          <t>16,22; 82,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>60,58; 98,71</t>
+          <t>61,86; 98,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,54; 95,1</t>
+          <t>59,83; 95,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40,76; 87,2</t>
+          <t>38,17; 87,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59,85; 94,03</t>
+          <t>61,94; 93,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,46; 94,41</t>
+          <t>60,4; 94,75</t>
         </is>
       </c>
     </row>
@@ -1276,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,35; 100,0</t>
+          <t>26,36; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,64; 100,0</t>
+          <t>39,1; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31,9; 100,0</t>
+          <t>31,88; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,34; 85,71</t>
+          <t>14,33; 85,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,15; 100,0</t>
+          <t>42,04; 92,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,17 +1312,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,24; 100,0</t>
+          <t>39,35; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,53; 86,24</t>
+          <t>33,73; 86,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57,02; 94,83</t>
+          <t>59,25; 95,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,14 +1332,14 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>54,21; 94,35</t>
+          <t>47,27; 94,28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,93; 87,64</t>
+          <t>13,12; 87,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,11; 55,31</t>
+          <t>8,2; 62,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,18; 100,0</t>
+          <t>28,44; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,33; 88,45</t>
+          <t>25,39; 88,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,94; 89,13</t>
+          <t>39,08; 91,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,79</t>
+          <t>0,0; 42,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31,78; 79,67</t>
+          <t>33,91; 81,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46,6; 92,01</t>
+          <t>39,23; 92,08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38,15; 80,78</t>
+          <t>37,3; 80,68</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,5; 40,49</t>
+          <t>4,79; 37,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39,9; 78,84</t>
+          <t>40,33; 79,36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,79; 92,61</t>
+          <t>41,72; 92,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41,93; 84,24</t>
+          <t>41,63; 84,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,7; 89,87</t>
+          <t>35,49; 91,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61,1; 96,46</t>
+          <t>62,48; 100,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,74; 91,24</t>
+          <t>54,63; 91,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,91; 91,92</t>
+          <t>55,49; 91,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,38; 65,37</t>
+          <t>14,53; 65,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>58,41; 89,18</t>
+          <t>57,48; 88,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>60,27; 86,28</t>
+          <t>57,75; 86,4</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55,97; 83,66</t>
+          <t>57,21; 83,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,27; 69,48</t>
+          <t>31,43; 70,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,55; 88,71</t>
+          <t>65,04; 89,22</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>35,88; 83,91</t>
+          <t>35,75; 82,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,96; 54,31</t>
+          <t>19,36; 56,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,66; 77,97</t>
+          <t>24,02; 78,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38,43; 91,93</t>
+          <t>40,88; 100,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>62,29; 91,09</t>
+          <t>62,39; 91,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,76; 62,04</t>
+          <t>28,37; 61,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,16; 78,33</t>
+          <t>25,42; 78,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,02; 79,77</t>
+          <t>18,46; 79,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58,96; 84,0</t>
+          <t>60,11; 83,64</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29,35; 54,36</t>
+          <t>29,01; 53,54</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35,4; 73,16</t>
+          <t>33,7; 73,59</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>38,41; 80,42</t>
+          <t>39,07; 79,59</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>59,04; 79,53</t>
+          <t>60,4; 80,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52,97; 70,41</t>
+          <t>53,45; 71,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39,66; 62,55</t>
+          <t>39,46; 64,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70,22; 88,39</t>
+          <t>70,86; 89,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>74,61; 87,96</t>
+          <t>75,03; 88,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55,32; 70,98</t>
+          <t>54,88; 71,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,35; 66,85</t>
+          <t>42,5; 65,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>66,16; 83,51</t>
+          <t>64,66; 82,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71,76; 83,16</t>
+          <t>71,64; 83,5</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56,39; 68,05</t>
+          <t>56,71; 68,39</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45,34; 61,22</t>
+          <t>44,71; 61,84</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>70,55; 83,15</t>
+          <t>69,98; 82,88</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5825</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10542</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5332</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13229</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10639</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11373</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5976</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>12885</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>16464</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21915</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11307</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>26114</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7607; 12867</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3250; 6485</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7775; 11349</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7673; 14348</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3122; 7938</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>10191; 13709</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>13649; 17174</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17527; 25941</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7696; 13787</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>22931; 26938</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4397</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6208</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5712</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9819</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8295</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2754</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3946</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>14217</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>14503</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>9658</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2039; 7117</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3561; 8822</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2593</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3176; 7307</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>7197; 11114</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4976; 10605</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>732; 3403</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1421; 6620</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>10248; 17365</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>10507; 17967</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1335; 5311</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5894; 12861</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4452</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7919</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5045</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2730</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6323</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9497</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>10650</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2123</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>12937</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5743; 9253</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3739</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4585; 7204</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>696; 4792</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2710</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3665; 7845</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7171; 13368</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>652; 4828</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>9338; 14928</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5127</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4217</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5517</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5993</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9566</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>19096</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11099</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>8036</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>15083</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>25089</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2846; 6611</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2683; 7710</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3023; 8420</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3662; 6804</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1258; 6405</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>13733; 21788</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>8027; 12768</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>4570; 10491</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>11577; 17527</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>19020; 29834</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3686</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4645</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2282</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2778</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6499</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6465</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>11145</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5832</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1380; 5237</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2094; 5355</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1020; 3200</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>700; 4187</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3574; 7886</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1262</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1633; 4151</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3414; 8712</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>8211; 13173</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1867</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3475; 6930</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2951</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2965</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>6217</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>6703</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>5276</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>9169</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>9668</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>764; 5106</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>604; 4591</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1189; 4181</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1273; 4443</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>3541; 8325</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3410</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>3916; 9386</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2782; 6531</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>5551; 12006</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>734; 5800</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>6344; 12484</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>6913</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>8196</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>4814</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8755</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>11666</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>13157</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>16994</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>18579</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>21352</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>8179</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>25749</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>4084; 9060</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>5399; 10940</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2625; 6751</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>6515; 10428</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>8228; 13766</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>9360; 15508</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1336; 6046</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>12704; 19483</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>14353; 21471</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>17070; 25027</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5215; 11646</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>21156; 29021</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>6920</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6595</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3916</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>18211</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>9917</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>4588</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>25130</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>16512</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>8504</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>9941</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>4111; 9468</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>3598; 10423</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1783; 5857</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>3405; 8330</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>14259; 20801</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>6246; 13645</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2127; 6554</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1488; 6439</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>20650; 28731</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>11777; 21735</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5322; 11620</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>6405; 13047</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>39396</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>51274</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>24192</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>51540</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>67331</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>62007</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>28429</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>73448</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>106727</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>113281</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>52621</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>124989</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>33568; 44653</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>43961; 58425</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>18596; 30253</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>45028; 56624</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>61625; 72284</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>53943; 70547</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>21865; 33701</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>64030; 82179</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>98650; 114986</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>102383; 123457</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>44075; 60958</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>113774; 134739</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09B02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -722,12 +722,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,88; 87,76</t>
+          <t>50,48; 87,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,95; 93,68</t>
+          <t>45,87; 93,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,51; 100,0</t>
+          <t>73,84; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,1; 86,21</t>
+          <t>43,74; 86,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,74; 88,33</t>
+          <t>35,25; 90,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74,34; 100,0</t>
+          <t>69,18; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79,47; 100,0</t>
+          <t>79,1; 100,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55,99; 82,87</t>
+          <t>55,76; 82,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48,38; 86,67</t>
+          <t>50,17; 87,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,13; 100,0</t>
+          <t>85,27; 100,0</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,21; 70,57</t>
+          <t>18,48; 67,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,27; 77,48</t>
+          <t>29,42; 77,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,4</t>
+          <t>0,0; 65,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,31; 95,02</t>
+          <t>40,45; 95,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,76; 100,0</t>
+          <t>64,83; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,11; 94,0</t>
+          <t>45,67; 90,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,52; 100,0</t>
+          <t>19,62; 100,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,22; 75,56</t>
+          <t>18,22; 75,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48,34; 81,91</t>
+          <t>49,44; 81,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46,35; 79,26</t>
+          <t>45,72; 78,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 75,48</t>
+          <t>17,93; 74,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,83; 78,18</t>
+          <t>37,0; 77,29</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,07; 100,0</t>
+          <t>56,21; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,28</t>
+          <t>0,0; 82,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63,64; 100,0</t>
+          <t>63,73; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,31; 77,86</t>
+          <t>11,25; 77,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,14; 92,36</t>
+          <t>39,85; 92,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,54; 86,75</t>
+          <t>46,98; 86,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,85; 65,53</t>
+          <t>8,09; 63,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59,49; 95,1</t>
+          <t>61,41; 95,24</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,05; 100,0</t>
+          <t>41,64; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,4; 84,48</t>
+          <t>28,84; 86,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,55; 90,67</t>
+          <t>32,5; 89,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,82; 100,0</t>
+          <t>44,51; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,22; 82,59</t>
+          <t>11,2; 80,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61,86; 98,13</t>
+          <t>63,22; 97,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,83; 95,17</t>
+          <t>60,39; 95,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38,17; 87,63</t>
+          <t>40,39; 88,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61,94; 93,77</t>
+          <t>58,79; 93,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,4; 94,75</t>
+          <t>59,75; 94,29</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,36; 100,0</t>
+          <t>26,35; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39,1; 100,0</t>
+          <t>42,36; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31,88; 100,0</t>
+          <t>31,86; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,04; 92,76</t>
+          <t>44,7; 92,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>39,35; 100,0</t>
+          <t>39,85; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,73; 86,07</t>
+          <t>35,05; 86,42</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59,25; 95,06</t>
+          <t>55,89; 95,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,27; 94,28</t>
+          <t>51,1; 94,06</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,12; 87,73</t>
+          <t>12,87; 87,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,2; 62,37</t>
+          <t>8,26; 63,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,44; 100,0</t>
+          <t>28,41; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,39; 88,58</t>
+          <t>26,01; 88,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,08; 91,87</t>
+          <t>37,69; 91,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,86</t>
+          <t>0,0; 42,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,91; 81,27</t>
+          <t>32,81; 79,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39,23; 92,08</t>
+          <t>43,97; 91,99</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37,3; 80,68</t>
+          <t>39,0; 80,68</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,79; 37,86</t>
+          <t>5,21; 39,57</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40,33; 79,36</t>
+          <t>39,07; 80,36</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,72; 92,56</t>
+          <t>42,04; 92,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41,63; 84,35</t>
+          <t>37,79; 84,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,49; 91,29</t>
+          <t>35,18; 91,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62,48; 100,0</t>
+          <t>57,42; 96,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,63; 91,39</t>
+          <t>54,84; 91,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,49; 91,93</t>
+          <t>55,26; 91,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,53; 65,75</t>
+          <t>14,29; 64,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>57,48; 88,16</t>
+          <t>59,13; 90,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>57,75; 86,4</t>
+          <t>60,51; 88,36</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57,21; 83,87</t>
+          <t>55,71; 83,81</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31,43; 70,2</t>
+          <t>28,99; 66,89</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,04; 89,22</t>
+          <t>66,01; 88,72</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>35,75; 82,34</t>
+          <t>34,06; 78,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,36; 56,1</t>
+          <t>18,89; 53,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,02; 78,9</t>
+          <t>24,44; 78,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40,88; 100,0</t>
+          <t>43,42; 92,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>62,39; 91,01</t>
+          <t>62,82; 91,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,37; 61,98</t>
+          <t>27,74; 63,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,42; 78,33</t>
+          <t>27,11; 79,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,46; 79,86</t>
+          <t>16,08; 76,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60,11; 83,64</t>
+          <t>59,6; 84,13</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29,01; 53,54</t>
+          <t>28,41; 52,57</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33,7; 73,59</t>
+          <t>34,61; 73,79</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>39,07; 79,59</t>
+          <t>40,75; 80,83</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>60,4; 80,35</t>
+          <t>60,24; 79,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>53,45; 71,04</t>
+          <t>54,06; 70,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39,46; 64,2</t>
+          <t>39,33; 62,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70,86; 89,1</t>
+          <t>71,89; 89,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>75,03; 88,01</t>
+          <t>74,32; 88,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,88; 71,78</t>
+          <t>55,36; 70,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42,5; 65,51</t>
+          <t>44,22; 66,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>64,66; 82,99</t>
+          <t>64,55; 83,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71,64; 83,5</t>
+          <t>71,47; 82,8</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56,71; 68,39</t>
+          <t>56,51; 67,83</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44,71; 61,84</t>
+          <t>46,0; 61,93</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>69,98; 82,88</t>
+          <t>70,47; 83,51</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7607; 12867</t>
+          <t>7401; 12854</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3250; 6485</t>
+          <t>3175; 6498</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2229,42 +2229,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7775; 11349</t>
+          <t>8380; 11349</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7673; 14348</t>
+          <t>7280; 14361</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3122; 7938</t>
+          <t>3168; 8133</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10191; 13709</t>
+          <t>9483; 13709</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13649; 17174</t>
+          <t>13585; 17174</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17527; 25941</t>
+          <t>17455; 25832</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7696; 13787</t>
+          <t>7981; 13929</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22931; 26938</t>
+          <t>22971; 26938</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2039; 7117</t>
+          <t>1864; 6830</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3561; 8822</t>
+          <t>3350; 8790</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2593</t>
+          <t>0; 2385</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3176; 7307</t>
+          <t>3111; 7315</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7197; 11114</t>
+          <t>7205; 11114</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4976; 10605</t>
+          <t>5153; 10206</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>732; 3403</t>
+          <t>668; 3403</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1421; 6620</t>
+          <t>1597; 6589</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10248; 17365</t>
+          <t>10481; 17321</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10507; 17967</t>
+          <t>10364; 17797</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1335; 5311</t>
+          <t>1262; 5259</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5894; 12861</t>
+          <t>6086; 12716</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5743; 9253</t>
+          <t>5201; 9253</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3739</t>
+          <t>0; 3861</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4585; 7204</t>
+          <t>4591; 7204</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>696; 4792</t>
+          <t>693; 4787</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3665; 7845</t>
+          <t>3385; 7871</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7171; 13368</t>
+          <t>7239; 13353</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>652; 4828</t>
+          <t>596; 4706</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9338; 14928</t>
+          <t>9640; 14952</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2846; 6611</t>
+          <t>2753; 6611</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2843,22 +2843,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2683; 7710</t>
+          <t>2632; 7891</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3023; 8420</t>
+          <t>3018; 8333</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3662; 6804</t>
+          <t>3028; 6804</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1258; 6405</t>
+          <t>869; 6205</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2868,27 +2868,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13733; 21788</t>
+          <t>14036; 21746</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8027; 12768</t>
+          <t>8101; 12780</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4570; 10491</t>
+          <t>4836; 10600</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11577; 17527</t>
+          <t>10990; 17433</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19020; 29834</t>
+          <t>18815; 29689</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2094; 5355</t>
+          <t>2269; 5355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1020; 3200</t>
+          <t>1019; 3200</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3574; 7886</t>
+          <t>3800; 7877</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1633; 4151</t>
+          <t>1654; 4151</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3414; 8712</t>
+          <t>3548; 8748</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8211; 13173</t>
+          <t>7745; 13189</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3475; 6930</t>
+          <t>3756; 6914</t>
         </is>
       </c>
     </row>
@@ -3254,57 +3254,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>764; 5106</t>
+          <t>749; 5104</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>604; 4591</t>
+          <t>608; 4653</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1189; 4181</t>
+          <t>1188; 4181</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1273; 4443</t>
+          <t>1305; 4431</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3541; 8325</t>
+          <t>3415; 8320</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3410</t>
+          <t>0; 3406</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3916; 9386</t>
+          <t>3790; 9135</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2782; 6531</t>
+          <t>3119; 6524</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5551; 12006</t>
+          <t>5805; 12006</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>734; 5800</t>
+          <t>798; 6062</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6344; 12484</t>
+          <t>6146; 12640</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4084; 9060</t>
+          <t>4115; 9056</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5399; 10940</t>
+          <t>4902; 10926</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2625; 6751</t>
+          <t>2602; 6749</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6515; 10428</t>
+          <t>5988; 10046</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8228; 13766</t>
+          <t>8260; 13769</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9360; 15508</t>
+          <t>9322; 15505</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1336; 6046</t>
+          <t>1314; 5917</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12704; 19483</t>
+          <t>13067; 19923</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14353; 21471</t>
+          <t>15036; 21959</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17070; 25027</t>
+          <t>16624; 25008</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5215; 11646</t>
+          <t>4810; 11098</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21156; 29021</t>
+          <t>21471; 28858</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4111; 9468</t>
+          <t>3916; 9049</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3598; 10423</t>
+          <t>3510; 9992</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1783; 5857</t>
+          <t>1814; 5859</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3405; 8330</t>
+          <t>3617; 7745</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14259; 20801</t>
+          <t>14358; 20876</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6246; 13645</t>
+          <t>6107; 13955</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2127; 6554</t>
+          <t>2268; 6617</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1488; 6439</t>
+          <t>1297; 6137</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>20650; 28731</t>
+          <t>20473; 28900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11777; 21735</t>
+          <t>11533; 21343</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5322; 11620</t>
+          <t>5465; 11651</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6405; 13047</t>
+          <t>6680; 13250</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>33568; 44653</t>
+          <t>33479; 44264</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>43961; 58425</t>
+          <t>44459; 58200</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18596; 30253</t>
+          <t>18533; 29516</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45028; 56624</t>
+          <t>45687; 56596</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>61625; 72284</t>
+          <t>61042; 72400</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>53943; 70547</t>
+          <t>54405; 69358</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21865; 33701</t>
+          <t>22748; 34242</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>64030; 82179</t>
+          <t>63923; 82207</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>98650; 114986</t>
+          <t>98413; 114016</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>102383; 123457</t>
+          <t>102009; 122446</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>44075; 60958</t>
+          <t>45337; 61043</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>113774; 134739</t>
+          <t>114571; 135763</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09B02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>93,74%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>68,33%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>66,5%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>93,83%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>71,91%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>77,02%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>93,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>66,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>93,99%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>95,86%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74,49; 100,0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>44,27; 85,58</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>39,05; 91,05</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>67,01; 100,0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>50,48; 87,67</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45,87; 93,87</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>51,59; 88,15</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,32; 93,3</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>73,84; 100,0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>43,74; 86,29</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>35,25; 90,51</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>69,18; 100,0</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79,1; 100,0</t>
+          <t>79,02; 100,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55,76; 82,52</t>
+          <t>55,12; 81,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50,17; 87,56</t>
+          <t>49,29; 86,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,27; 100,0</t>
+          <t>78,98; 100,0</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>88,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>73,52%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>80,92%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>48,25%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>43,6%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>54,52%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>15,71%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>74,28%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>88,35%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>73,52%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>80,92%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,48; 67,72</t>
+          <t>64,89; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,42; 77,2</t>
+          <t>46,6; 94,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,66</t>
+          <t>20,24; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,45; 95,12</t>
+          <t>14,96; 77,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,83; 100,0</t>
+          <t>18,12; 70,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,67; 90,46</t>
+          <t>30,12; 77,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,62; 100,0</t>
+          <t>0,0; 65,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,22; 75,2</t>
+          <t>44,75; 95,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49,44; 81,7</t>
+          <t>50,28; 81,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,72; 78,51</t>
+          <t>46,68; 79,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,93; 74,74</t>
+          <t>18,43; 75,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,0; 77,29</t>
+          <t>40,56; 80,73</t>
         </is>
       </c>
     </row>
@@ -934,44 +934,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>44,35%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24,73%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>72,74%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>85,58%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>31,2%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>91,01%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>44,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>74,44%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>69,11%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56,21; 100,0</t>
+          <t>11,16; 77,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,9</t>
+          <t>0,0; 75,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63,73; 100,0</t>
+          <t>39,6; 91,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,25; 77,77</t>
+          <t>55,93; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 80,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,85; 92,66</t>
+          <t>62,55; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,98; 86,65</t>
+          <t>46,25; 86,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,09; 63,88</t>
+          <t>8,2; 65,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>61,41; 95,24</t>
+          <t>60,0; 95,18</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87,77%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49,25%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>86,23%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>77,55%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>60,45%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>64,54%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>87,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,25%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,64; 100,0</t>
+          <t>43,01; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>14,97; 81,07</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>28,84; 86,47</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,5; 89,74</t>
+          <t>62,09; 98,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,51; 100,0</t>
+          <t>40,13; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,2; 80,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,41; 86,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,22; 97,95</t>
+          <t>32,51; 91,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,39; 95,27</t>
+          <t>59,54; 95,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40,39; 88,54</t>
+          <t>40,76; 87,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58,79; 93,27</t>
+          <t>59,85; 94,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,75; 94,29</t>
+          <t>61,06; 93,73</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56,88%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>76,44%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52,48%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86,19%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>70,39%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>86,75%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>71,31%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>56,88%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>76,44%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>52,48%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14,34; 85,71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>44,15; 100,0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54,55; 100,0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>26,35; 100,0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>42,36; 100,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>43,64; 100,0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>31,86; 100,0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,33; 85,71</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>44,7; 92,65</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>32,17; 100,0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>34,53; 86,24</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>57,02; 94,83</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>39,85; 100,0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>35,05; 86,42</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>55,89; 95,17</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,1; 94,06</t>
+          <t>53,91; 93,96</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63,8%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>68,61%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>57,73%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>50,71%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>26,96%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>70,91%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>63,8%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>25,33; 88,45</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>37,94; 89,13</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 42,79</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31,24; 80,57</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>12,87; 87,7</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>8,26; 63,2</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>28,41; 100,0</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>26,01; 88,34</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,69; 91,82</t>
+          <t>12,93; 87,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,8</t>
+          <t>8,11; 55,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,81; 79,1</t>
+          <t>27,33; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43,97; 91,99</t>
+          <t>46,6; 92,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39,0; 80,68</t>
+          <t>38,15; 80,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,21; 39,57</t>
+          <t>5,5; 40,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39,07; 80,36</t>
+          <t>40,65; 79,32</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>77,45%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>78,0%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36,6%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>76,74%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>70,63%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>63,19%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>65,1%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>83,95%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>77,45%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>78,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>36,6%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,42%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,04; 92,53</t>
+          <t>54,74; 91,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,79; 84,24</t>
+          <t>56,91; 91,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,18; 91,27</t>
+          <t>14,38; 65,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57,42; 96,34</t>
+          <t>57,45; 89,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,84; 91,41</t>
+          <t>41,79; 92,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,26; 91,92</t>
+          <t>41,93; 84,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,29; 64,34</t>
+          <t>28,7; 89,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>59,13; 90,15</t>
+          <t>59,35; 96,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>60,51; 88,36</t>
+          <t>60,27; 86,28</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55,71; 83,81</t>
+          <t>55,97; 83,66</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28,99; 66,89</t>
+          <t>29,27; 69,48</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,01; 88,72</t>
+          <t>66,39; 88,67</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>79,68%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>45,04%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>54,84%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46,98%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>60,18%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>35,49%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>52,76%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>71,92%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>79,68%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>45,04%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>54,84%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>58,95%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>34,06; 78,69</t>
+          <t>62,29; 91,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,89; 53,78</t>
+          <t>27,76; 62,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,44; 78,93</t>
+          <t>24,16; 78,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43,42; 92,97</t>
+          <t>18,07; 80,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>62,82; 91,34</t>
+          <t>35,88; 83,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,74; 63,39</t>
+          <t>17,96; 54,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,11; 79,08</t>
+          <t>22,66; 77,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,08; 76,11</t>
+          <t>36,11; 92,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>59,6; 84,13</t>
+          <t>58,96; 84,0</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28,41; 52,57</t>
+          <t>29,35; 54,36</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34,61; 73,79</t>
+          <t>35,4; 73,16</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>40,75; 80,83</t>
+          <t>36,36; 79,68</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>81,98%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>63,09%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>73,91%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>70,89%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>62,34%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>51,34%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>81,1%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>81,98%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>63,09%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>55,26%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>60,24; 79,65</t>
+          <t>74,61; 87,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54,06; 70,77</t>
+          <t>55,32; 70,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39,33; 62,64</t>
+          <t>43,35; 66,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>71,89; 89,06</t>
+          <t>65,36; 82,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>74,32; 88,15</t>
+          <t>59,04; 79,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55,36; 70,57</t>
+          <t>52,97; 70,41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,22; 66,56</t>
+          <t>39,66; 62,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>64,55; 83,01</t>
+          <t>69,21; 86,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71,47; 82,8</t>
+          <t>71,76; 83,16</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56,51; 67,83</t>
+          <t>56,39; 68,05</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46,0; 61,93</t>
+          <t>45,34; 61,22</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>70,47; 83,51</t>
+          <t>69,61; 82,22</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10639</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11373</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5976</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10834</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>5825</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>10542</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>5332</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13229</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10639</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11373</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5976</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12885</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26114</t>
+          <t>18565</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8454; 11349</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7368; 14242</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3509; 8182</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7738; 11546</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7401; 12854</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3175; 6498</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7563; 12924</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3137; 6458</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8380; 11349</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7280; 14361</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3168; 8133</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9483; 13709</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13585; 17174</t>
+          <t>13571; 17174</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17455; 25832</t>
+          <t>17256; 25640</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7981; 13929</t>
+          <t>7841; 13809</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22971; 26938</t>
+          <t>15226; 19277</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9819</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8295</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2754</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3612</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4397</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6208</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>570</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5712</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9819</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8295</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2754</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>9646</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1864; 6830</t>
+          <t>7212; 11114</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3350; 8790</t>
+          <t>5258; 10618</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2385</t>
+          <t>689; 3403</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3111; 7315</t>
+          <t>1120; 5796</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7205; 11114</t>
+          <t>1828; 7138</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5153; 10206</t>
+          <t>3429; 8835</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>668; 3403</t>
+          <t>0; 2383</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1597; 6589</t>
+          <t>3520; 7546</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10481; 17321</t>
+          <t>10659; 17367</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10364; 17797</t>
+          <t>10582; 18079</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1262; 5259</t>
+          <t>1297; 5313</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6086; 12716</t>
+          <t>6227; 12393</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5045</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2730</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4452</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>7919</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1453</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6614</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5045</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2730</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12937</t>
+          <t>11312</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5201; 9253</t>
+          <t>687; 4793</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3861</t>
+          <t>0; 2048</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4591; 7204</t>
+          <t>2895; 6667</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>693; 4787</t>
+          <t>5175; 9253</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2710</t>
+          <t>0; 3761</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3385; 7871</t>
+          <t>4120; 6587</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7239; 13353</t>
+          <t>7127; 13330</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>596; 4706</t>
+          <t>604; 4832</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9640; 14952</t>
+          <t>8339; 13227</t>
         </is>
       </c>
     </row>
@@ -2702,37 +2702,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9566</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>16736</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5127</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4217</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>5517</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5993</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5972</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3819</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9566</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19096</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>23448</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2753; 6611</t>
+          <t>2926; 6804</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>1161; 6287</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2632; 7891</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3018; 8333</t>
+          <t>12051; 19075</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3028; 6804</t>
+          <t>2653; 6611</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>869; 6205</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2684; 7912</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14036; 21746</t>
+          <t>3291; 9288</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8101; 12780</t>
+          <t>7988; 12757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4836; 10600</t>
+          <t>4880; 10440</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10990; 17433</t>
+          <t>11187; 17577</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18815; 29689</t>
+          <t>18031; 27680</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2778</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6499</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3564</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>3686</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>4645</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2282</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2778</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6499</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>5876</t>
         </is>
       </c>
     </row>
@@ -3041,52 +3041,52 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>701; 4187</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3753; 8502</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1262</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2256; 4135</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>1380; 5237</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2269; 5355</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2337; 5355</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1019; 3200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>700; 4187</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3800; 7877</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0; 1262</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1654; 4151</t>
+          <t>1075; 3341</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3548; 8748</t>
+          <t>3495; 8729</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7745; 13189</t>
+          <t>7903; 13141</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3756; 6914</t>
+          <t>4031; 7024</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6217</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5547</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2076</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2951</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1985</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2965</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3200</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>6217</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>848</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>8687</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>1271; 4436</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3438; 8077</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3405</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>3002; 7741</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>749; 5104</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>608; 4653</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1188; 4181</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1305; 4431</t>
-        </is>
-      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3415; 8320</t>
+          <t>753; 5101</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3406</t>
+          <t>597; 4072</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3790; 9135</t>
+          <t>1224; 4478</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3119; 6524</t>
+          <t>3305; 6526</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5805; 12006</t>
+          <t>5677; 12021</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>798; 6062</t>
+          <t>843; 6202</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6146; 12640</t>
+          <t>5726; 11174</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>11666</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>13157</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>16169</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>6913</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>8196</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>4814</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>8755</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>11666</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>13157</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>3365</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25749</t>
+          <t>25215</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4115; 9056</t>
+          <t>8245; 13743</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4902; 10926</t>
+          <t>9601; 15506</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2602; 6749</t>
+          <t>1323; 6011</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5988; 10046</t>
+          <t>12105; 18815</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8260; 13769</t>
+          <t>4091; 9065</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9322; 15505</t>
+          <t>5438; 10925</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1314; 5917</t>
+          <t>2122; 6646</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13067; 19923</t>
+          <t>6338; 10357</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15036; 21959</t>
+          <t>14979; 21442</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16624; 25008</t>
+          <t>16701; 24961</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4810; 11098</t>
+          <t>4856; 11527</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21471; 28858</t>
+          <t>21080; 28153</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>18211</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>9917</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>4588</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3903</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>6920</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>6595</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>3916</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5991</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>18211</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>9917</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>4588</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9778</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3916; 9049</t>
+          <t>14236; 20818</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3510; 9992</t>
+          <t>6112; 13660</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1814; 5859</t>
+          <t>2021; 6554</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3617; 7745</t>
+          <t>1501; 6658</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14358; 20876</t>
+          <t>4125; 9649</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6107; 13955</t>
+          <t>3338; 10092</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2268; 6617</t>
+          <t>1682; 5788</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1297; 6137</t>
+          <t>2988; 7667</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>20473; 28900</t>
+          <t>20255; 28858</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11533; 21343</t>
+          <t>11916; 22066</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5465; 11651</t>
+          <t>5589; 11553</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6680; 13250</t>
+          <t>6030; 13215</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>67331</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>62007</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>28429</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>65683</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>39396</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>51274</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>24192</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>51540</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>67331</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>62007</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>28429</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>73448</t>
+          <t>46842</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>124989</t>
+          <t>112525</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>33479; 44264</t>
+          <t>61277; 72241</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>44459; 58200</t>
+          <t>54369; 69759</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18533; 29516</t>
+          <t>22300; 34394</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45687; 56596</t>
+          <t>58089; 73728</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>61042; 72400</t>
+          <t>32809; 44199</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>54405; 69358</t>
+          <t>43562; 57908</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22748; 34242</t>
+          <t>18689; 29474</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>63923; 82207</t>
+          <t>40889; 51248</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>98413; 114016</t>
+          <t>98818; 114513</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>102009; 122446</t>
+          <t>101791; 122853</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45337; 61043</t>
+          <t>44687; 60342</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>114571; 135763</t>
+          <t>102983; 121641</t>
         </is>
       </c>
     </row>
